--- a/data/trans_bre/P16A11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,89</t>
+          <t>4,58; 12,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,72</t>
+          <t>3,77; 12,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,52</t>
+          <t>3,09; 12,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 17,88</t>
+          <t>8,56; 17,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 50,73</t>
+          <t>16,6; 51,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 36,53</t>
+          <t>10,28; 37,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 44,13</t>
+          <t>9,56; 43,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,55; 53,61</t>
+          <t>21,57; 52,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,34</t>
+          <t>-1,95; 1,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,74</t>
+          <t>-3,06; 0,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,2</t>
+          <t>-1,99; 2,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 29,51</t>
+          <t>-2,24; 28,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 24,67</t>
+          <t>-26,98; 23,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 8,88</t>
+          <t>-29,46; 11,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 22,86</t>
+          <t>-17,05; 22,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 217,98</t>
+          <t>-15,51; 235,24</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,23</t>
+          <t>-5,23; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,63</t>
+          <t>-6,69; 0,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,84</t>
+          <t>-7,34; -0,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -3,58</t>
+          <t>-9,91; -3,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 20,37</t>
+          <t>-55,56; 16,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 13,11</t>
+          <t>-58,1; 12,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,51; -7,76</t>
+          <t>-64,9; -7,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,19; -23,32</t>
+          <t>-52,31; -21,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,65</t>
+          <t>2,25; 5,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,28</t>
+          <t>2,27; 6,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,84</t>
+          <t>1,04; 4,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 20,7</t>
+          <t>1,34; 21,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 47,7</t>
+          <t>16,41; 48,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 40,08</t>
+          <t>12,67; 39,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 34,66</t>
+          <t>7,1; 33,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 135,76</t>
+          <t>7,27; 131,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,06</t>
+          <t>4,22; 12,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 12,05</t>
+          <t>3,63; 11,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,41</t>
+          <t>4,0; 12,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 17,68</t>
+          <t>8,72; 17,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 51,47</t>
+          <t>15,53; 51,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 37,4</t>
+          <t>9,55; 36,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 43,96</t>
+          <t>12,16; 45,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,57; 52,62</t>
+          <t>22,36; 55,75</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>-12,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,29</t>
+          <t>-2,15; 1,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,95</t>
+          <t>-2,96; 0,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,24</t>
+          <t>-1,97; 2,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 28,33</t>
+          <t>-3,89; -0,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 23,03</t>
+          <t>-29,02; 23,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 11,84</t>
+          <t>-28,65; 10,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 22,81</t>
+          <t>-16,95; 22,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 235,24</t>
+          <t>-23,72; -1,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,74</t>
+          <t>-6,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-39,99%</t>
+          <t>-36,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,98</t>
+          <t>-5,18; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,77</t>
+          <t>-7,03; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; -0,75</t>
+          <t>-7,1; -0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -3,04</t>
+          <t>-9,58; -3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 16,75</t>
+          <t>-52,82; 19,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 12,68</t>
+          <t>-62,75; 7,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,9; -7,99</t>
+          <t>-64,82; -2,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,31; -21,27</t>
+          <t>-49,86; -20,98</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,83</t>
+          <t>2,31; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,06</t>
+          <t>2,31; 6,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,67</t>
+          <t>1,13; 4,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 21,99</t>
+          <t>0,02; 3,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 48,5</t>
+          <t>17,09; 48,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 39,05</t>
+          <t>13,05; 39,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 33,75</t>
+          <t>7,34; 33,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 131,43</t>
+          <t>0,16; 19,08</t>
         </is>
       </c>
     </row>
